--- a/survey_templates/033_two_wheeler_user_experience_survey--survey_templates.xlsx
+++ b/survey_templates/033_two_wheeler_user_experience_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'walk'}</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Walk'}</t>
+          <t>Walk</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'bike'}</t>
+          <t>bike</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Bike'}</t>
+          <t>Bike</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly Agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Agree'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'neither_agree_nor_disagree'}</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Neither Agree nor Disagree'}</t>
+          <t>Neither Agree nor Disagree</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly Disagree'}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Disagree'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'1-3_months'}</t>
+          <t>1-3_months</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': '1-3 months'}</t>
+          <t>1-3 months</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'1-6_months'}</t>
+          <t>1-6_months</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': '1-6 months'}</t>
+          <t>1-6 months</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'6_months_-_1_year'}</t>
+          <t>6_months_-_1_year</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': '6 months - 1 year'}</t>
+          <t>6 months - 1 year</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'1-2_years'}</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': '1-2 years'}</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'2-3_years'}</t>
+          <t>2-3_years</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': '2-3 years'}</t>
+          <t>2-3 years</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'3-5_years'}</t>
+          <t>3-5_years</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': '3-5 years'}</t>
+          <t>3-5 years</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'5_years_or_more'}</t>
+          <t>5_years_or_more</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': '5 years or more'}</t>
+          <t>5 years or more</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly Agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Agree'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'neither_agree_nor_disagree'}</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Neither Agree nor Disagree'}</t>
+          <t>Neither Agree nor Disagree</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly Disagree'}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Disagree'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'walk'}</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Walk'}</t>
+          <t>Walk</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'bike'}</t>
+          <t>bike</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Bike'}</t>
+          <t>Bike</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
